--- a/NuevasNotas/Vespertina/Resultados_Auditoria_Notas/Matriz_Marcada_4BV.xlsx
+++ b/NuevasNotas/Vespertina/Resultados_Auditoria_Notas/Matriz_Marcada_4BV.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,10 +58,16 @@
       <sz val="12"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -91,24 +97,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="003B82F6"/>
+        <bgColor rgb="003B82F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E5E7EB"/>
         <bgColor rgb="00E5E7EB"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F3F4F6"/>
-        <bgColor rgb="00F3F4F6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -207,11 +207,16 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -252,19 +257,23 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -767,13 +776,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -785,736 +795,577 @@
       <c r="B1" s="16" t="n"/>
       <c r="C1" s="16" t="n"/>
       <c r="D1" s="16" t="n"/>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Curso</t>
-        </is>
-      </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="E1" s="16" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>▶ CURSO: 4BV</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>Estudiante</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>Tipo de Problema</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
-        <is>
-          <t>Detalle de la Discrepancia</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>Materia</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>Docente</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>ASMAL CAJAMARCA PAULA LIZETH</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
-        <is>
-          <t>Inglés (Docente: 9.28 vs Sistema: 6.26)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="20" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B4" s="21" t="inlineStr">
-        <is>
-          <t>ASMAL CAJAMARCA PAULA LIZETH</t>
-        </is>
-      </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>6.26</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="21" t="n"/>
+      <c r="B6" s="21" t="n"/>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="E6" s="23" t="n">
+        <v>8.779999999999999</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>BANEGAS SIMBAÑA JOSE DARIO</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>⚠️ FALTA EN DOCENTE</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>(Nómina)</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>CABRERA RODRIGUEZ DANNIA ARACELY</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 9.19 vs Sistema: 8.78)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>BANEGAS SIMBAÑA JOSE DARIO</t>
-        </is>
-      </c>
-      <c r="C5" s="18" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN DOCENTE</t>
-        </is>
-      </c>
-      <c r="D5" s="19" t="inlineStr">
-        <is>
-          <t>El estudiante está en el reporte oficial pero falta en la matriz del docente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="25" customHeight="1">
-      <c r="A6" s="20" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>BARZALLO BUESTAN ARIEL SEBASTIAN</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="25" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>BUENO BORJA PABLO JOSUE</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="25" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>BUENO FERNANDEZ MARIA BELEN</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="25" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>CABRERA PESANTEZ ROBERTO EMANUEL</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="25" customHeight="1">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>CABRERA RODRIGUEZ DANNIA ARACELY</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="25" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>CABRERA RODRIGUEZ DANNIA ARACELY</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="E8" s="23" t="n">
+        <v>9.32</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>CALDERON GRANDA JARED FAVIAN</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>⚠️ FALTA EN SISTEMA</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>(Nómina)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>GARCIA LARRAZABAL FRANCIS ALEXANDER</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 9.41 vs Sistema: 9.32)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="25" customHeight="1">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t>CALDERON GRANDA JARED FAVIAN</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN SISTEMA</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t>El estudiante está en la matriz del docente pero no en el reporte oficial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="25" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>GARCIA LARRAZABAL FRANCIS ALEXANDER</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="E10" s="23" t="n">
+        <v>9.06</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>GUACHICHULLCA ZHUNIO SANTIAGO ALEJANDRO</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 9.14 vs Sistema: 9.06)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="25" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>GUACHICHULLCA ZHUNIO SANTIAGO ALEJANDRO</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="25" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>GUACHICHULLCA ZHUNIO SANTIAGO ALEJANDRO</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="E11" s="23" t="n">
+        <v>8.81</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>HURTADO CALLE SCARLETT SAMIRA</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 8.76 vs Sistema: 8.81)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="25" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>GUARTAN CHILLOGALLI NAYELI MARILU</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="25" customHeight="1">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>HURTADO CALLE SCARLETT SAMIRA</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="E12" s="23" t="n">
+        <v>8.43</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>JAPA GUACHICHULLCA DALILA JAMILETH</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 8.3 vs Sistema: 8.43)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="25" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>JAPA GUACHICHULLCA DALILA JAMILETH</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="E13" s="23" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>MAUREL APONCIO CHARLES ANTONIO</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 8.61 vs Sistema: 8.7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="25" customHeight="1">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>MAUREL APONCIO CHARLES ANTONIO</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="E14" s="23" t="n">
+        <v>8.779999999999999</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>MERCHAN LUNA MATIEL ISRAEL</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 8.81 vs Sistema: 8.78)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="25" customHeight="1">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B20" s="21" t="inlineStr">
-        <is>
-          <t>MENDEZ ORDOÑEZ BRITHANY KASSANDRA</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="25" customHeight="1">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>MERCHAN LUNA MATIEL ISRAEL</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="25" customHeight="1">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>MERCHAN LUNA MATIEL ISRAEL</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="E15" s="23" t="n">
+        <v>8.44</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>MORQUECHO ORELLANA MIKAELA ARACELY</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 8.52 vs Sistema: 8.44)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="25" customHeight="1">
-      <c r="A23" s="18" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>MORQUECHO ORELLANA MIKAELA ARACELY</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="E16" s="23" t="n">
+        <v>8.19</v>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>NARANJO HERNANDEZ ELIAS EZEQUIEL</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D23" s="19" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 8.22 vs Sistema: 8.19)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="25" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B24" s="21" t="inlineStr">
-        <is>
-          <t>NARANJO HERNANDEZ ELIAS EZEQUIEL</t>
-        </is>
-      </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="E17" s="23" t="n">
+        <v>7.57</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>PAUCAR AUCAPIÑA MATIAS EFRAIN</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 7.54 vs Sistema: 7.57)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="25" customHeight="1">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>PAUCAR AUCAPIÑA MATIAS EFRAIN</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="E18" s="23" t="n">
+        <v>9.74</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>PEREZ SINCHI MATIAS FERNANDO</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D25" s="19" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 9.78 vs Sistema: 9.74)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="25" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B26" s="21" t="inlineStr">
-        <is>
-          <t>PEREZ SINCHI MATIAS FERNANDO</t>
-        </is>
-      </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="E19" s="23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>POMA SARAGURO KARLA VALENTINA</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 8.83 vs Sistema: 8.8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="25" customHeight="1">
-      <c r="A27" s="18" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>POMA SARAGURO KARLA VALENTINA</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="E20" s="23" t="n">
+        <v>8.390000000000001</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>ROMERO NACIPUCHA LUIS ESTEBAN</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D27" s="19" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 8.35 vs Sistema: 8.39)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="25" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B28" s="21" t="inlineStr">
-        <is>
-          <t>ROMERO NACIPUCHA LUIS ESTEBAN</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="E21" s="23" t="n">
+        <v>8.07</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>SINCHI MUÑOZ RUBEN DARIO</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 8.11 vs Sistema: 8.07)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="25" customHeight="1">
-      <c r="A29" s="18" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B29" s="19" t="inlineStr">
-        <is>
-          <t>SINCHI MUÑOZ RUBEN DARIO</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="E22" s="23" t="n">
+        <v>8.34</v>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>TIGRE QUITO JHOANNA LIZETH</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D29" s="19" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 8.3 vs Sistema: 8.34)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="25" customHeight="1">
-      <c r="A30" s="20" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B30" s="21" t="inlineStr">
-        <is>
-          <t>TIGRE QUITO JHOANNA LIZETH</t>
-        </is>
-      </c>
-      <c r="C30" s="20" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="E23" s="23" t="n">
+        <v>9.039999999999999</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>TORRES AROTINGO ANTHONY JOEL</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 9.0 vs Sistema: 9.04)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="25" customHeight="1">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="inlineStr">
-        <is>
-          <t>TORRES AROTINGO ANTHONY JOEL</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="E24" s="23" t="n">
+        <v>8.58</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>ZHIZHPON CORTE JOSTIN PAUL</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D31" s="19" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 8.52 vs Sistema: 8.58)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="25" customHeight="1">
-      <c r="A32" s="20" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B32" s="21" t="inlineStr">
-        <is>
-          <t>ZHIZHPON CORTE JOSTIN PAUL</t>
-        </is>
-      </c>
-      <c r="C32" s="20" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="E25" s="23" t="n">
+        <v>9.35</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>ZHUNIO QUITO MATIAS JOSUE</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D32" s="21" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 9.44 vs Sistema: 9.35)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="25" customHeight="1">
-      <c r="A33" s="18" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B33" s="19" t="inlineStr">
-        <is>
-          <t>ZHUNIO QUITO MATIAS JOSUE</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="E26" s="23" t="n">
+        <v>8.710000000000001</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>ZUMBA CAGUANA EMERSON JOAO</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D33" s="19" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 8.62 vs Sistema: 8.71)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="25" customHeight="1">
-      <c r="A34" s="20" t="inlineStr">
-        <is>
-          <t>4BV</t>
-        </is>
-      </c>
-      <c r="B34" s="21" t="inlineStr">
-        <is>
-          <t>ZUMBA CAGUANA EMERSON JOAO</t>
-        </is>
-      </c>
-      <c r="C34" s="20" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D34" s="21" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 9.22 vs Sistema: 9.25)</t>
-        </is>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="E27" s="23" t="n">
+        <v>9.25</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+  <mergeCells count="4">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
